--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -37820,18 +37820,18 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -37841,14 +37841,14 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>-6</v>
@@ -37874,18 +37874,18 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -37895,14 +37895,14 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>-6</v>
@@ -37982,41 +37982,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H29" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.0135</v>
@@ -38025,7 +38025,7 @@
         <v>0.6565</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="30">
@@ -38090,41 +38090,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0135</v>
@@ -38133,7 +38133,7 @@
         <v>0.6565</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -39062,23 +39062,23 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -39096,7 +39096,7 @@
         <v>7</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.8617</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -39150,7 +39150,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.8617</v>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>L. TOURE</t>
+          <t>E. SOLE SANCHEZ</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -39343,7 +39343,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
@@ -39375,7 +39375,7 @@
         <v>0.8621</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="55">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>E. SOLE SANCHEZ</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -39411,7 +39411,7 @@
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
@@ -39429,7 +39429,7 @@
         <v>0.8621</v>
       </c>
       <c r="N55" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>L. TOURE</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -40304,18 +40304,18 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -40338,7 +40338,7 @@
         <v>2</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
         <v>2</v>
@@ -40412,7 +40412,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>C. GONZALEZ PLANELLA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -40466,30 +40466,30 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>C. GONZALEZ PLANELLA</t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H75" s="8" t="n">
         <v>0</v>
       </c>
@@ -40500,7 +40500,7 @@
         <v>2</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>S. KOSAREVA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -40682,7 +40682,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>S. KOSAREVA</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -40736,7 +40736,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -37604,41 +37604,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -37647,7 +37647,7 @@
         <v>1.011</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="23">
@@ -37658,41 +37658,41 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -37701,7 +37701,7 @@
         <v>1.011</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -37820,35 +37820,35 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>-6</v>
@@ -37928,35 +37928,35 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>-6</v>
@@ -37982,23 +37982,23 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -38007,10 +38007,10 @@
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>6</v>
@@ -38025,7 +38025,7 @@
         <v>0.6565</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -38036,28 +38036,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H30" s="8" t="n">
@@ -38070,7 +38070,7 @@
         <v>6</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>1.0135</v>
@@ -38090,41 +38090,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.0135</v>
@@ -38133,7 +38133,7 @@
         <v>0.6565</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="32">
@@ -38954,28 +38954,28 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
@@ -39062,18 +39062,18 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -39096,7 +39096,7 @@
         <v>7</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.8617</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -39150,7 +39150,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.8617</v>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>E. SOLE SANCHEZ</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
@@ -39375,7 +39375,7 @@
         <v>0.8621</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>L. TOURE</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -39397,7 +39397,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>L. TOURE</t>
+          <t>E. SOLE SANCHEZ</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -39465,7 +39465,7 @@
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
@@ -39483,7 +39483,7 @@
         <v>0.8621</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="57">
@@ -39494,14 +39494,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -39548,14 +39548,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -39602,14 +39602,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -39656,14 +39656,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -40088,7 +40088,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>C. GONZALEZ PLANELLA</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -40358,7 +40358,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRIETO PEREDA </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -40412,7 +40412,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>C. GONZALEZ PLANELLA</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRIETO PEREDA </t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -40736,7 +40736,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -6685,7 +6685,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -6779,16 +6779,16 @@
         <v>0</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>0.4138</v>
+        <v>0.4211</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>0.0314</v>
+        <v>0.0387</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>0.6333</v>
+        <v>0.5556</v>
       </c>
       <c r="AJ22" s="6" t="n">
-        <v>0.0236</v>
+        <v>-0.0542</v>
       </c>
     </row>
     <row r="23">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -6893,16 +6893,16 @@
         <v>0</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>0.4211</v>
+        <v>0.4138</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>0.0387</v>
+        <v>0.0314</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>0.5556</v>
+        <v>0.6333</v>
       </c>
       <c r="AJ23" s="6" t="n">
-        <v>-0.0542</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="24">
@@ -37604,41 +37604,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L22" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -37647,7 +37647,7 @@
         <v>1.011</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -37658,41 +37658,41 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -37701,7 +37701,7 @@
         <v>1.011</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="24">
@@ -37874,18 +37874,18 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -37895,14 +37895,14 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>-6</v>
@@ -37928,18 +37928,18 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -37949,14 +37949,14 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>-6</v>
@@ -38954,28 +38954,28 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
@@ -39008,7 +39008,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -39029,7 +39029,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -39062,18 +39062,18 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -39083,7 +39083,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -39096,7 +39096,7 @@
         <v>7</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.8617</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -39150,7 +39150,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.8617</v>
@@ -39170,7 +39170,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>M. ALONSO GUADAÑO</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -39278,7 +39278,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. ALONSO GUADAÑO</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>E. SOLE SANCHEZ</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>0</v>
@@ -39375,7 +39375,7 @@
         <v>0.8621</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="55">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>E. SOLE SANCHEZ</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -39465,7 +39465,7 @@
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>0</v>
@@ -39483,7 +39483,7 @@
         <v>0.8621</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -39548,14 +39548,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -39656,14 +39656,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -40088,7 +40088,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -40412,30 +40412,30 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H74" s="8" t="n">
         <v>0</v>
       </c>
@@ -40446,7 +40446,7 @@
         <v>2</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>2</v>
@@ -40466,18 +40466,18 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -40500,7 +40500,7 @@
         <v>2</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>2</v>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>S. KOSAREVA</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -40682,7 +40682,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>S. KOSAREVA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -40736,7 +40736,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -8985,7 +8985,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -9079,16 +9079,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>0.2963</v>
+        <v>0.3506</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>-0.0485</v>
+        <v>0.0058</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>0.6038</v>
+        <v>0.6129</v>
       </c>
       <c r="AJ24" s="6" t="n">
-        <v>-0.0244</v>
+        <v>-0.0153</v>
       </c>
     </row>
     <row r="25">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -9193,16 +9193,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.3506</v>
+        <v>0.2963</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>0.0058</v>
+        <v>-0.0485</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6129</v>
+        <v>0.6038</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>-0.0153</v>
+        <v>-0.0244</v>
       </c>
     </row>
     <row r="26">
@@ -54682,28 +54682,28 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
@@ -54716,7 +54716,7 @@
         <v>6</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.0135</v>
@@ -54736,41 +54736,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -54779,7 +54779,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -54790,35 +54790,35 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>6</v>
@@ -54833,7 +54833,7 @@
         <v>0.6565</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="38">
@@ -56032,7 +56032,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>L. TOURE</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -56043,7 +56043,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -56086,7 +56086,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>L. TOURE</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -56097,7 +56097,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -56410,7 +56410,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -56518,7 +56518,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56583,7 +56583,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -56788,18 +56788,18 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -56809,7 +56809,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
@@ -56822,7 +56822,7 @@
         <v>7</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>1.8617</v>
@@ -56896,23 +56896,23 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -56930,7 +56930,7 @@
         <v>7</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>1.8617</v>
@@ -56950,28 +56950,28 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. ALONSO GUADAÑO</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57058,7 +57058,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. ALONSO GUADAÑO</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -57166,14 +57166,14 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57220,14 +57220,14 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
@@ -57274,14 +57274,14 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
@@ -57328,14 +57328,14 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -58138,7 +58138,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>S. KOSAREVA</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -58192,7 +58192,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>S. KOSAREVA</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -54196,41 +54196,41 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54239,7 +54239,7 @@
         <v>1.011</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -54250,41 +54250,41 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L27" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54293,7 +54293,7 @@
         <v>1.011</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="28">
@@ -54520,35 +54520,35 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>-6</v>
@@ -54628,35 +54628,35 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>-6</v>
@@ -54682,35 +54682,35 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>6</v>
@@ -54725,7 +54725,7 @@
         <v>0.6565</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="36">
@@ -54736,28 +54736,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
@@ -54770,7 +54770,7 @@
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -54790,41 +54790,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.0135</v>
@@ -54833,7 +54833,7 @@
         <v>0.6565</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -56410,7 +56410,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -56518,7 +56518,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -56529,7 +56529,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56788,28 +56788,28 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
@@ -56842,7 +56842,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -56863,7 +56863,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
@@ -56896,18 +56896,18 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -56917,7 +56917,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
@@ -56930,7 +56930,7 @@
         <v>7</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>1.8617</v>
@@ -56950,28 +56950,28 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -56984,7 +56984,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>1.8617</v>
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. ALONSO GUADAÑO</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57058,7 +57058,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>M. ALONSO GUADAÑO</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -57166,7 +57166,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57274,14 +57274,14 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
@@ -57328,14 +57328,14 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -57760,7 +57760,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -58138,7 +58138,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>S. KOSAREVA</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -58192,7 +58192,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>S. KOSAREVA</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -54520,14 +54520,14 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -54536,12 +54536,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
@@ -54574,18 +54574,18 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -54595,14 +54595,14 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>-6</v>
@@ -54628,35 +54628,35 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>-6</v>
@@ -54736,28 +54736,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
@@ -54770,7 +54770,7 @@
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -54790,28 +54790,28 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
@@ -54824,7 +54824,7 @@
         <v>6</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.0135</v>
@@ -56518,7 +56518,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -56529,7 +56529,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56583,7 +56583,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -56788,28 +56788,28 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
@@ -56822,7 +56822,7 @@
         <v>7</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>1.8617</v>
@@ -56896,28 +56896,28 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
@@ -56950,18 +56950,18 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -56971,7 +56971,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -56984,7 +56984,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>1.8617</v>
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. ALONSO GUADAÑO</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57112,7 +57112,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. ALONSO GUADAÑO</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -57166,14 +57166,14 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57328,14 +57328,14 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -57760,7 +57760,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -54196,41 +54196,41 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54239,7 +54239,7 @@
         <v>1.011</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="27">
@@ -54250,41 +54250,41 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L27" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54293,7 +54293,7 @@
         <v>1.011</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -54520,18 +54520,18 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -54541,14 +54541,14 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>-6</v>
@@ -54574,35 +54574,35 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>-6</v>
@@ -54628,14 +54628,14 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -54644,12 +54644,12 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -54682,41 +54682,41 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.0135</v>
@@ -54725,7 +54725,7 @@
         <v>0.6565</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -54736,41 +54736,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -54779,7 +54779,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="37">
@@ -56410,7 +56410,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56583,7 +56583,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -56788,7 +56788,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -56809,7 +56809,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
@@ -56842,23 +56842,23 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -56876,7 +56876,7 @@
         <v>7</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>1.8617</v>
@@ -56896,28 +56896,28 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
@@ -56950,18 +56950,18 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -56971,7 +56971,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -56984,7 +56984,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>1.8617</v>
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57058,7 +57058,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -57166,14 +57166,14 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57274,14 +57274,14 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -57760,7 +57760,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -58138,7 +58138,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -8985,7 +8985,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -9079,16 +9079,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>0.3506</v>
+        <v>0.2963</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>0.0058</v>
+        <v>-0.0485</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>0.6129</v>
+        <v>0.6038</v>
       </c>
       <c r="AJ24" s="6" t="n">
-        <v>-0.0153</v>
+        <v>-0.0244</v>
       </c>
     </row>
     <row r="25">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -9193,16 +9193,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.2963</v>
+        <v>0.3506</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>-0.0485</v>
+        <v>0.0058</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6038</v>
+        <v>0.6129</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>-0.0244</v>
+        <v>-0.0153</v>
       </c>
     </row>
     <row r="26">
@@ -54034,18 +54034,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -54068,7 +54068,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>1.2739</v>
@@ -54088,18 +54088,18 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -54122,7 +54122,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="L24" s="11" t="n">
         <v>1.2739</v>
@@ -54520,35 +54520,35 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>-6</v>
@@ -54574,35 +54574,35 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>-6</v>
@@ -56410,7 +56410,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -56464,7 +56464,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>V. GAUNA</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -56475,7 +56475,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -56518,7 +56518,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>V. GAUNA</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -56529,7 +56529,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56896,18 +56896,18 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -56917,7 +56917,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
@@ -56930,7 +56930,7 @@
         <v>7</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
         <v>1.8617</v>
@@ -56950,18 +56950,18 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -56971,7 +56971,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -56984,7 +56984,7 @@
         <v>7</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
         <v>1.8617</v>
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57058,7 +57058,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. ALONSO GUADAÑO</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -57112,7 +57112,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>M. ALONSO GUADAÑO</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -57166,14 +57166,14 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57220,14 +57220,14 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
@@ -57274,7 +57274,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>A. PEREZ RELANCIO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>A. PEREZ RELANCIO</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -58138,7 +58138,7 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>S. KOSAREVA</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -58192,7 +58192,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>S. KOSAREVA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -54034,18 +54034,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -54068,7 +54068,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>1.2739</v>
@@ -54088,18 +54088,18 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -54122,7 +54122,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="L24" s="11" t="n">
         <v>1.2739</v>
@@ -54196,41 +54196,41 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54239,7 +54239,7 @@
         <v>1.011</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -54250,41 +54250,41 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L27" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -54293,7 +54293,7 @@
         <v>1.011</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="28">
@@ -54520,14 +54520,14 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -54536,12 +54536,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
@@ -54628,14 +54628,14 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -54644,12 +54644,12 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -54682,41 +54682,41 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.0135</v>
@@ -54725,7 +54725,7 @@
         <v>0.6565</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="36">
@@ -54736,23 +54736,23 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -54761,10 +54761,10 @@
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
@@ -54779,7 +54779,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -54790,28 +54790,28 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
@@ -54824,7 +54824,7 @@
         <v>6</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.0135</v>
@@ -56032,7 +56032,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>L. TOURE</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -56043,7 +56043,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -56086,7 +56086,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>L. TOURE</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -56097,7 +56097,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -56410,7 +56410,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -56518,7 +56518,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>V. GAUNA</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -56529,7 +56529,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -56572,7 +56572,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>V. GAUNA</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -56583,7 +56583,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -56788,18 +56788,18 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -56809,7 +56809,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
@@ -56822,7 +56822,7 @@
         <v>7</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>1.8617</v>
@@ -56842,23 +56842,23 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -56876,7 +56876,7 @@
         <v>7</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
         <v>1.8617</v>
@@ -56950,28 +56950,28 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>I. ARAÚJO GOUVEIA VIEIRA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
@@ -57004,7 +57004,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -57112,7 +57112,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -57166,14 +57166,14 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
@@ -57220,14 +57220,14 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
@@ -57274,7 +57274,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -57760,7 +57760,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -58030,7 +58030,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>E. ASPAJO GIL</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -58192,7 +58192,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>E. ASPAJO GIL</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -60887,35 +60887,35 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
@@ -60930,7 +60930,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="37">
@@ -60941,23 +60941,23 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -60966,10 +60966,10 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>6</v>
@@ -60984,7 +60984,7 @@
         <v>0.6565</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -61589,41 +61589,41 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.0997</v>
@@ -61632,7 +61632,7 @@
         <v>1.1411</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>0</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="50">
@@ -61643,41 +61643,41 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.0997</v>
@@ -61686,7 +61686,7 @@
         <v>1.1411</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>0.0733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -63101,14 +63101,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>E. JACQUOT</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -63122,17 +63122,17 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="K77" s="10" t="n">
         <v>0</v>
@@ -63141,10 +63141,10 @@
         <v>0.6944</v>
       </c>
       <c r="M77" s="9" t="n">
-        <v>1.8519</v>
+        <v>1.8908</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0.6944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>M. GERKE</t>
+          <t>E. JACQUOT</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -63180,13 +63180,13 @@
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="K78" s="10" t="n">
         <v>0</v>
@@ -63195,10 +63195,10 @@
         <v>0.6944</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>1.8908</v>
+        <v>1.8519</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="79">
@@ -63209,14 +63209,14 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>M. GERKE</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
@@ -63230,7 +63230,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H79" s="8" t="n">
@@ -63371,7 +63371,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -63382,7 +63382,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -63425,7 +63425,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -63436,7 +63436,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -63533,7 +63533,7 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -63857,14 +63857,14 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
@@ -63965,7 +63965,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -63986,7 +63986,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
@@ -64019,14 +64019,14 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
@@ -64721,7 +64721,7 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ LLAMAZARES</t>
+          <t>A. BOQUETE MANNA</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
@@ -64732,12 +64732,12 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -64829,7 +64829,7 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>A. BOQUETE MANNA</t>
+          <t>A. MARTIN CASTAÑEDA</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
@@ -64840,12 +64840,12 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -64937,7 +64937,7 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTAÑEDA</t>
+          <t>J. MARTINEZ LLAMAZARES</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -60671,18 +60671,18 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -60692,14 +60692,14 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>-6</v>
@@ -60725,14 +60725,14 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -60741,12 +60741,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
@@ -60779,35 +60779,35 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>-6</v>
@@ -60833,28 +60833,28 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
@@ -60867,7 +60867,7 @@
         <v>6</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.0135</v>
@@ -60887,41 +60887,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -60930,7 +60930,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -60941,35 +60941,35 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>6</v>
@@ -60984,7 +60984,7 @@
         <v>0.6565</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="38">
@@ -61535,7 +61535,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -61551,12 +61551,12 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -61569,7 +61569,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0997</v>
@@ -61589,41 +61589,41 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.0997</v>
@@ -61632,7 +61632,7 @@
         <v>1.1411</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>0.0733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -61643,41 +61643,41 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.0997</v>
@@ -61686,7 +61686,7 @@
         <v>1.1411</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>0</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="51">
@@ -62723,7 +62723,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>L. TOURE</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -62734,7 +62734,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -62777,7 +62777,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>L. TOURE</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -62788,7 +62788,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -63101,14 +63101,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. TERRER VAN GOOL</t>
+          <t>E. JACQUOT</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -63122,17 +63122,17 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="K77" s="10" t="n">
         <v>0</v>
@@ -63141,10 +63141,10 @@
         <v>0.6944</v>
       </c>
       <c r="M77" s="9" t="n">
-        <v>1.8908</v>
+        <v>1.8519</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="78">
@@ -63155,14 +63155,14 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>E. JACQUOT</t>
+          <t>M. TERRER VAN GOOL</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -63176,17 +63176,17 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="8" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="K78" s="10" t="n">
         <v>0</v>
@@ -63195,10 +63195,10 @@
         <v>0.6944</v>
       </c>
       <c r="M78" s="9" t="n">
-        <v>1.8519</v>
+        <v>1.8908</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0.6944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63965,14 +63965,14 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
@@ -64019,14 +64019,14 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
@@ -64775,18 +64775,18 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>L. MELERO SABAT</t>
+          <t>A. MARTIN CASTAÑEDA</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -64809,7 +64809,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
         <v>2</v>
@@ -64829,18 +64829,18 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTAÑEDA</t>
+          <t>L. MELERO SABAT</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -64863,7 +64863,7 @@
         <v>1</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="9" t="n">
         <v>2</v>

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -10609,16 +10609,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.3506</v>
+        <v>0.2963</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>0.0058</v>
+        <v>-0.0485</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6129</v>
+        <v>0.6038</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>-0.0153</v>
+        <v>-0.0244</v>
       </c>
     </row>
     <row r="26">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -10723,16 +10723,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0.2963</v>
+        <v>0.3506</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>-0.0485</v>
+        <v>0.0058</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.6038</v>
+        <v>0.6129</v>
       </c>
       <c r="AJ26" s="6" t="n">
-        <v>-0.0244</v>
+        <v>-0.0153</v>
       </c>
     </row>
     <row r="27">
@@ -60185,18 +60185,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -60206,7 +60206,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -60219,7 +60219,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>1.2739</v>
@@ -60239,18 +60239,18 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -60260,7 +60260,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -60273,7 +60273,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="L24" s="11" t="n">
         <v>1.2739</v>
@@ -60347,41 +60347,41 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S. GALERON ALVAREZ</t>
+          <t>S. SAMUEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -60390,7 +60390,7 @@
         <v>1.011</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -60401,41 +60401,41 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>S. SAMUEL</t>
+          <t>S. GALERON ALVAREZ</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>10.2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>-3</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="L27" s="11" t="n">
         <v>0.9350000000000001</v>
@@ -60444,7 +60444,7 @@
         <v>1.011</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="28">
@@ -60833,28 +60833,28 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
@@ -60867,7 +60867,7 @@
         <v>6</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.0135</v>
@@ -60887,41 +60887,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.0135</v>
@@ -60930,7 +60930,7 @@
         <v>0.6565</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="37">
@@ -60941,23 +60941,23 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -60966,10 +60966,10 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>6</v>
@@ -60984,7 +60984,7 @@
         <v>0.6565</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -61535,7 +61535,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -61551,12 +61551,12 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -61569,7 +61569,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0997</v>
@@ -61589,7 +61589,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -61605,12 +61605,12 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -61623,7 +61623,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1.0997</v>
@@ -63857,7 +63857,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -63878,7 +63878,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
@@ -63911,7 +63911,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -63965,7 +63965,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -64019,7 +64019,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -64040,7 +64040,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
@@ -64721,7 +64721,7 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>A. BOQUETE MANNA</t>
+          <t>J. MARTINEZ LLAMAZARES</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
@@ -64732,12 +64732,12 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -64775,7 +64775,7 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTAÑEDA</t>
+          <t>P. VAQUERA BLANCO</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -64829,30 +64829,30 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>L. MELERO SABAT</t>
+          <t>A. BOQUETE MANNA</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H109" s="8" t="n">
         <v>0</v>
       </c>
@@ -64863,7 +64863,7 @@
         <v>1</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
         <v>2</v>
@@ -64883,7 +64883,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>P. VAQUERA BLANCO</t>
+          <t>A. MARTIN CASTAÑEDA</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -64937,18 +64937,18 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ LLAMAZARES</t>
+          <t>L. MELERO SABAT</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -64971,7 +64971,7 @@
         <v>1</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="9" t="n">
         <v>2</v>

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -12055,16 +12055,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.32</v>
+        <v>0.3592</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>-0.039</v>
+        <v>0.0002</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6364</v>
+        <v>0.6768</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>-0.033</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="26">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -12169,16 +12169,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0.3592</v>
+        <v>0.32</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>0.0002</v>
+        <v>-0.039</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.6768</v>
+        <v>0.6364</v>
       </c>
       <c r="AJ26" s="6" t="n">
-        <v>0.0074</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="27">
@@ -66221,18 +66221,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -66242,7 +66242,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -66255,7 +66255,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="n">
         <v>1.2739</v>
@@ -66275,18 +66275,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -66309,7 +66309,7 @@
         <v>6</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="L32" s="11" t="n">
         <v>1.2739</v>
@@ -66923,35 +66923,35 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>-6</v>
@@ -66977,35 +66977,35 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>-6</v>
@@ -67895,23 +67895,23 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -67929,7 +67929,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L62" s="9" t="n">
         <v>1.2731</v>
@@ -67949,23 +67949,23 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -67983,7 +67983,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
         <v>1.2731</v>
@@ -68489,7 +68489,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>S. CASTRO</t>
+          <t>D. DÍAZ GÓMEZ</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -68517,7 +68517,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>0</v>
@@ -68543,7 +68543,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>D. DÍAZ GÓMEZ</t>
+          <t>S. CASTRO</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -68571,7 +68571,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>0</v>
@@ -69029,7 +69029,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -69040,7 +69040,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -69083,7 +69083,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -69094,7 +69094,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -69893,14 +69893,14 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>A. DIEZ PASTOR</t>
+          <t>C. LANGARITA HERNANDEZ</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
@@ -69909,12 +69909,12 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
@@ -69947,14 +69947,14 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>C. LANGARITA HERNANDEZ</t>
+          <t>A. DIEZ PASTOR</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
@@ -69963,12 +69963,12 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
@@ -70001,7 +70001,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>C. PINTO</t>
+          <t>M. AKULLU</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -70055,18 +70055,18 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>R. COTANO DE JUAN</t>
+          <t>C. PINTO</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -70089,7 +70089,7 @@
         <v>-4</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
         <v>0.6667</v>
@@ -70109,18 +70109,18 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>N. DIARRA BERTHE</t>
+          <t>R. COTANO DE JUAN</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -70143,7 +70143,7 @@
         <v>-4</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="9" t="n">
         <v>0.6667</v>
@@ -70163,7 +70163,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>M. AKULLU</t>
+          <t>N. DIARRA BERTHE</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -70649,14 +70649,14 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
@@ -70670,7 +70670,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
@@ -70703,14 +70703,14 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
@@ -70724,7 +70724,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
@@ -70757,7 +70757,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -70778,7 +70778,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
@@ -71027,7 +71027,7 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>M. ROSALES ELEJABEITA</t>
+          <t>M. HERMOSO JIMENEZ</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
@@ -71058,7 +71058,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="8" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="K120" s="10" t="n">
         <v>0</v>
@@ -71067,7 +71067,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>2</v>
+        <v>2.0833</v>
       </c>
       <c r="N120" s="10" t="n">
         <v>0</v>
@@ -71081,7 +71081,7 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>M. HERMOSO JIMENEZ</t>
+          <t>M. ROSALES ELEJABEITA</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -71112,7 +71112,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="8" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="K121" s="10" t="n">
         <v>0</v>
@@ -71121,7 +71121,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>2.0833</v>
+        <v>2</v>
       </c>
       <c r="N121" s="10" t="n">
         <v>0</v>
@@ -71351,7 +71351,7 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -71405,7 +71405,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -12055,16 +12055,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.3592</v>
+        <v>0.32</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>0.0002</v>
+        <v>-0.039</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6768</v>
+        <v>0.6364</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>0.0074</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="26">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -12169,16 +12169,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0.32</v>
+        <v>0.3592</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>-0.039</v>
+        <v>0.0002</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.6364</v>
+        <v>0.6768</v>
       </c>
       <c r="AJ26" s="6" t="n">
-        <v>-0.033</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="27">
@@ -66221,18 +66221,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t>N. LISTE ALFONSIN</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -66242,7 +66242,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -66255,7 +66255,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="L31" s="11" t="n">
         <v>1.2739</v>
@@ -66275,18 +66275,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N. LISTE ALFONSIN</t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
@@ -66309,7 +66309,7 @@
         <v>6</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="L32" s="11" t="n">
         <v>1.2739</v>
@@ -66869,18 +66869,18 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -66890,14 +66890,14 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-6</v>
@@ -66923,14 +66923,14 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -66939,12 +66939,12 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
@@ -66977,35 +66977,35 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>-6</v>
@@ -67031,28 +67031,28 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N. DIMITRIJEVIC </t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
@@ -67065,7 +67065,7 @@
         <v>6</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>1.0135</v>
@@ -67085,28 +67085,28 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t xml:space="preserve">N. DIMITRIJEVIC </t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
@@ -67119,7 +67119,7 @@
         <v>6</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="9" t="n">
         <v>1.0135</v>
@@ -67625,7 +67625,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -67641,12 +67641,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -67659,7 +67659,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L57" s="9" t="n">
         <v>1.0997</v>
@@ -67679,7 +67679,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -67695,12 +67695,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -67713,7 +67713,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>1.0997</v>
@@ -68975,18 +68975,18 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -68996,20 +68996,20 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
         <v>0.8721</v>
@@ -69029,7 +69029,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -69040,7 +69040,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -69083,41 +69083,41 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
         <v>0.8721</v>
@@ -70001,18 +70001,18 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>M. AKULLU</t>
+          <t>R. COTANO DE JUAN</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -70035,7 +70035,7 @@
         <v>-4</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="9" t="n">
         <v>0.6667</v>
@@ -70109,18 +70109,18 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>R. COTANO DE JUAN</t>
+          <t>M. AKULLU</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -70143,7 +70143,7 @@
         <v>-4</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
         <v>0.6667</v>
@@ -70649,14 +70649,14 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
@@ -70670,7 +70670,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
@@ -70703,14 +70703,14 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
@@ -70724,7 +70724,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
@@ -70811,7 +70811,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -71351,7 +71351,7 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>J. CARMONA ALONSO</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
@@ -71405,7 +71405,7 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>J. CARMONA ALONSO</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -12055,16 +12055,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.32</v>
+        <v>0.3592</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>-0.039</v>
+        <v>0.0002</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6364</v>
+        <v>0.6768</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>-0.033</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="26">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -12169,16 +12169,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0.3592</v>
+        <v>0.32</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>0.0002</v>
+        <v>-0.039</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.6768</v>
+        <v>0.6364</v>
       </c>
       <c r="AJ26" s="6" t="n">
-        <v>0.0074</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="27">
@@ -66869,35 +66869,35 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-6</v>
@@ -66923,18 +66923,18 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -66944,14 +66944,14 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>-6</v>
@@ -66977,14 +66977,14 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -66993,12 +66993,12 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
@@ -67031,41 +67031,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H46" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>1.0135</v>
@@ -67074,7 +67074,7 @@
         <v>0.6565</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="47">
@@ -67139,41 +67139,41 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0135</v>
@@ -67182,7 +67182,7 @@
         <v>0.6565</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -67625,7 +67625,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R. LEHTORANTA </t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -67641,12 +67641,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -67659,7 +67659,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
         <v>1.0997</v>
@@ -67679,7 +67679,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t xml:space="preserve">R. LEHTORANTA </t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -67695,12 +67695,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -67713,7 +67713,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>1.0997</v>
@@ -68975,18 +68975,18 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>C. GARCIA PAUNERO</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -68996,20 +68996,20 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="9" t="n">
         <v>0.8721</v>
@@ -69083,18 +69083,18 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>C. GARCIA PAUNERO</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -69104,20 +69104,20 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
         <v>0.8721</v>
@@ -69893,14 +69893,14 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>C. LANGARITA HERNANDEZ</t>
+          <t>A. DIEZ PASTOR</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
@@ -69909,12 +69909,12 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
@@ -69947,14 +69947,14 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>A. DIEZ PASTOR</t>
+          <t>C. LANGARITA HERNANDEZ</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
@@ -69963,12 +69963,12 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
@@ -70001,18 +70001,18 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>R. COTANO DE JUAN</t>
+          <t>M. AKULLU</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -70035,7 +70035,7 @@
         <v>-4</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
         <v>0.6667</v>
@@ -70055,18 +70055,18 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>C. PINTO</t>
+          <t>R. COTANO DE JUAN</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -70089,7 +70089,7 @@
         <v>-4</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="9" t="n">
         <v>0.6667</v>
@@ -70109,7 +70109,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>M. AKULLU</t>
+          <t>N. DIARRA BERTHE</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -70163,7 +70163,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>N. DIARRA BERTHE</t>
+          <t>C. PINTO</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -70649,7 +70649,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>E. MORALES LÓPEZ</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -70703,14 +70703,14 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>L. ROIG I SALRACH</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
@@ -70724,7 +70724,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
@@ -70757,7 +70757,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. ROIG I SALRACH</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -70778,7 +70778,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
@@ -70811,14 +70811,14 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>E. MORALES LÓPEZ</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
@@ -70832,7 +70832,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H116" s="8" t="n">
@@ -71729,18 +71729,18 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTAÑEDA</t>
+          <t>L. MELERO SABAT</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -71763,7 +71763,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="9" t="n">
         <v>2</v>
@@ -71783,18 +71783,18 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>L. MELERO SABAT</t>
+          <t>A. MARTIN CASTAÑEDA</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -71817,7 +71817,7 @@
         <v>1</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
         <v>2</v>

--- a/fulls/full_mestre_challenge_2026.xlsx
+++ b/fulls/full_mestre_challenge_2026.xlsx
@@ -11961,7 +11961,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. PRATTER </t>
+          <t xml:space="preserve">M. BARATA SILVA </t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -12055,16 +12055,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0.3592</v>
+        <v>0.32</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>0.0002</v>
+        <v>-0.039</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0.6768</v>
+        <v>0.6364</v>
       </c>
       <c r="AJ25" s="6" t="n">
-        <v>0.0074</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="26">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M. BARATA SILVA </t>
+          <t xml:space="preserve">C. PRATTER </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -12169,16 +12169,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0.32</v>
+        <v>0.3592</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>-0.039</v>
+        <v>0.0002</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>0.6364</v>
+        <v>0.6768</v>
       </c>
       <c r="AJ26" s="6" t="n">
-        <v>-0.033</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="27">
@@ -66869,35 +66869,35 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. JACKSON </t>
+          <t>L. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>-6</v>
@@ -66923,18 +66923,18 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>L. CAMPOS DE BENGOA</t>
+          <t>T. DA SILVA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -66944,14 +66944,14 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>-6</v>
@@ -66977,14 +66977,14 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>T. DA SILVA</t>
+          <t xml:space="preserve">B. JACKSON </t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -66993,12 +66993,12 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
@@ -67031,41 +67031,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>M. NGNAWO NGUIENSAM</t>
+          <t>N. RIOS MAQUEDA</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>1.0135</v>
@@ -67074,7 +67074,7 @@
         <v>0.6565</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -67139,41 +67139,41 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>N. RIOS MAQUEDA</t>
+          <t>M. NGNAWO NGUIENSAM</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0135</v>
@@ -67182,7 +67182,7 @@
         <v>0.6565</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="49">
@@ -67625,41 +67625,41 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>A. SENOSIAIN VERGARACHEA</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
       <c r="H57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="L57" s="9" t="n">
         <v>1.0997</v>
@@ -67668,7 +67668,7 @@
         <v>1.1411</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>0</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="58">
@@ -67733,41 +67733,41 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A. SENOSIAIN VERGARACHEA</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="L59" s="9" t="n">
         <v>1.0997</v>
@@ -67776,7 +67776,7 @@
         <v>1.1411</v>
       </c>
       <c r="N59" s="10" t="n">
-        <v>0.0733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -67895,23 +67895,23 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>K. BENITEZ DE LA ROSA</t>
+          <t>L. SOARES JOSEFINO</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -67929,7 +67929,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
         <v>1.2731</v>
@@ -67949,23 +67949,23 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>L. SOARES JOSEFINO</t>
+          <t>K. BENITEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -67983,7 +67983,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L63" s="9" t="n">
         <v>1.2731</v>
@@ -68489,7 +68489,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>D. DÍAZ GÓMEZ</t>
+          <t>S. CASTRO</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -68517,7 +68517,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>0</v>
@@ -68543,7 +68543,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>S. CASTRO</t>
+          <t>D. DÍAZ GÓMEZ</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -68571,7 +68571,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>0</v>
@@ -68975,18 +68975,18 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>M. BLANCO MORCILLO</t>
+          <t>A. WONE ARANAZ</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -68996,20 +68996,20 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
         <v>0.8721</v>
@@ -69029,41 +69029,41 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>A. WONE ARANAZ</t>
+          <t>M. BLANCO MORCILLO</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="9" t="n">
         <v>0.8721</v>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>M. AKULLU</t>
+          <t>N. DIARRA BERTHE</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -70109,7 +70109,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>N. DIARRA BERTHE</t>
+          <t>M. AKULLU</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -70703,14 +70703,14 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>L. SOLER MADARIAGA</t>
+          <t>M. AGUADO TORTELLA</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
@@ -70724,7 +70724,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
@@ -70811,14 +70811,14 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>M. AGUADO TORTELLA</t>
+          <t>L. SOLER MADARIAGA</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
@@ -70832,7 +70832,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H116" s="8" t="n">
@@ -71729,18 +71729,18 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>L. MELERO SABAT</t>
+          <t>A. MARTIN CASTAÑEDA</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -71763,7 +71763,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
         <v>2</v>
@@ -71783,18 +71783,18 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTAÑEDA</t>
+          <t>L. MELERO SABAT</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -71817,7 +71817,7 @@
         <v>1</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
         <v>2</v>
